--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.67526</v>
+        <v>17.03763</v>
       </c>
       <c r="D2" t="n">
-        <v>16.85211</v>
+        <v>16.9232</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01204</v>
+        <v>16.94313</v>
       </c>
       <c r="F2" t="n">
-        <v>43.32467</v>
+        <v>43.1534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05183</v>
+        <v>0.05052</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84398</v>
+        <v>1.88824</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90055</v>
+        <v>16.94399</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90127</v>
+        <v>16.88291</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9501</v>
+        <v>16.93331</v>
       </c>
       <c r="F3" t="n">
-        <v>42.96998</v>
+        <v>42.94258</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05015</v>
+        <v>0.05108</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83448</v>
+        <v>1.83537</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.90634</v>
+        <v>16.99122</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69742</v>
+        <v>16.78454</v>
       </c>
       <c r="E4" t="n">
-        <v>17.09621</v>
+        <v>16.83635</v>
       </c>
       <c r="F4" t="n">
-        <v>42.97081</v>
+        <v>43.37506</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05076</v>
+        <v>0.05181</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86647</v>
+        <v>1.82963</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63343</v>
+        <v>17.06621</v>
       </c>
       <c r="D6" t="n">
-        <v>15.97713</v>
+        <v>16.09711</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41382</v>
+        <v>16.40925</v>
       </c>
       <c r="F6" t="n">
-        <v>22.01206</v>
+        <v>22.24957</v>
       </c>
       <c r="G6" t="n">
-        <v>34.67294</v>
+        <v>34.89199</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84491</v>
+        <v>17.03623</v>
       </c>
       <c r="D7" t="n">
-        <v>16.67255</v>
+        <v>16.20584</v>
       </c>
       <c r="E7" t="n">
-        <v>16.26283</v>
+        <v>16.72915</v>
       </c>
       <c r="F7" t="n">
-        <v>22.48696</v>
+        <v>21.96511</v>
       </c>
       <c r="G7" t="n">
-        <v>35.00801</v>
+        <v>34.661</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.94134</v>
+        <v>16.68092</v>
       </c>
       <c r="D8" t="n">
-        <v>16.22932</v>
+        <v>15.99255</v>
       </c>
       <c r="E8" t="n">
-        <v>16.66941</v>
+        <v>16.66242</v>
       </c>
       <c r="F8" t="n">
-        <v>21.86377</v>
+        <v>21.98848</v>
       </c>
       <c r="G8" t="n">
-        <v>35.10713</v>
+        <v>35.19604</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61064</v>
+        <v>0.61295</v>
       </c>
       <c r="D10" t="n">
-        <v>1.13142</v>
+        <v>1.10964</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61561</v>
+        <v>0.62164</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1257</v>
+        <v>1.12083</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60721</v>
+        <v>0.6118400000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11397</v>
+        <v>1.10753</v>
       </c>
     </row>
   </sheetData>
